--- a/AAII_Financials/Quarterly/TPG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TPG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>TPG</t>
   </si>
@@ -656,212 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1736000</v>
+      </c>
+      <c r="E8" s="3">
         <v>409900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1384500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1111900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>825800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>947800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>989800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>772800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>744200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>824100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>983100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>160400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>603300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>643100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>420000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>563000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>909700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1117400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1098900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>745900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2340800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1359100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1568800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>902200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1207000</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -886,27 +893,27 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>552800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>630700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>712900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>139000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>442900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>499100</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -943,53 +950,56 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1736000</v>
+      </c>
+      <c r="E10" s="3">
         <v>409900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1384500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1111900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>825800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>947800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>989800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>772800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>191400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>193400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>270200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>160400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>144100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,53 +1240,56 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E14" s="3">
         <v>1100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
-        <v>800</v>
-      </c>
       <c r="H14" s="3">
-        <v>2100</v>
+        <v>3800</v>
       </c>
       <c r="I14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>16700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1306,80 +1326,83 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E15" s="3">
         <v>41800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>41300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>41000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>31400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>37900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>33000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>23400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>17300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16100</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="3">
         <v>1800</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1392000</v>
+      </c>
+      <c r="E17" s="3">
         <v>558500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1118300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>919700</v>
       </c>
-      <c r="G17" s="3">
-        <v>795400</v>
-      </c>
       <c r="H17" s="3">
-        <v>860800</v>
+        <v>792400</v>
       </c>
       <c r="I17" s="3">
+        <v>851900</v>
+      </c>
+      <c r="J17" s="3">
         <v>1011600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>784500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>755000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>815300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>907900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>248300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>555800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>612200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>429500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>518600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>996700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>942500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>299000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>224200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>198700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>194600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>191600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>177000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>192900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>256000</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>344100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-148600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>266200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>192200</v>
       </c>
-      <c r="G18" s="3">
-        <v>30400</v>
-      </c>
       <c r="H18" s="3">
-        <v>87000</v>
+        <v>33400</v>
       </c>
       <c r="I18" s="3">
+        <v>95900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-21800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>75200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-88000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>47500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>31000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>44400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-87000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>174900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>799900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>521700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2142100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1164500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1377200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>725200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1014100</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1646,36 +1680,36 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>500</v>
       </c>
       <c r="P20" s="3">
         <v>500</v>
       </c>
       <c r="Q20" s="3">
+        <v>500</v>
+      </c>
+      <c r="R20" s="3">
         <v>8700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>10400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>36800</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1683,105 +1717,111 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-229500</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
+      <c r="AB20" s="3">
+        <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>385400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-106800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>307500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>233200</v>
       </c>
-      <c r="G21" s="3">
-        <v>61200</v>
-      </c>
       <c r="H21" s="3">
-        <v>118400</v>
+        <v>64200</v>
       </c>
       <c r="I21" s="3">
+        <v>127300</v>
+      </c>
+      <c r="J21" s="3">
         <v>16100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>20700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>41800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>98600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-80400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>55400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>38700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>52500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-68000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>186500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>853000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>1155400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>730900</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1806,27 +1846,27 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>21500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7400</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1863,174 +1903,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>356000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-140700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>304900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>228100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>39300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>94200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-35200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>69200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-86500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>53200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>47800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>53600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-76600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>177800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>836700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>521800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2142100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1164400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1147700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>725200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1014000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1438200</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-17400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>22500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>28900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>22400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>26800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>15000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2100</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>319700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-123300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>282400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>199200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>87800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-57600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>42400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-94700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>40000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>53200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-99700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>162800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>833800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>520500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2140400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1161300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1143800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>723500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1012000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1440300</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-8000</v>
+        <v>72700</v>
       </c>
       <c r="E27" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="F27" s="3">
         <v>65900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>49300</v>
       </c>
-      <c r="G27" s="3">
-        <v>-16800</v>
-      </c>
       <c r="H27" s="3">
-        <v>25400</v>
+        <v>4400</v>
       </c>
       <c r="I27" s="3">
+        <v>8500</v>
+      </c>
+      <c r="J27" s="3">
         <v>3600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>25500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>21200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>22200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>41700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>325900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>294800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>890900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>514200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>608200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>323100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>606300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-610000</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2642,36 +2712,36 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-500</v>
       </c>
       <c r="P32" s="3">
         <v>-500</v>
       </c>
       <c r="Q32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R32" s="3">
         <v>-8700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-10400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-36800</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2679,105 +2749,111 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>229500</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
+      <c r="AB32" s="3">
+        <v>0</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>93400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>77100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>67100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>25400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>15500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>26600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>22200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>30000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>41700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>325900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>294800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>890900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>514200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>608200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>323100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>606300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-610000</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>93400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>77100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>67100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>25400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>15500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>26600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>22200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>30000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>41700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>325900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>294800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>890900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>514200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>608200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>323100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>606300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-610000</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,71 +3178,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>944700</v>
+      </c>
+      <c r="E41" s="3">
         <v>851400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>826100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1080300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1112000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>822000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>808000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1164500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1121000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1090700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>665200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1224500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>897600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>936300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1112600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1058900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1185300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1464100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>978100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1787400</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3262,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,71 +3348,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>427700</v>
+      </c>
+      <c r="E43" s="3">
         <v>367700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>573600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>361100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>387700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>308000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>447000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>317700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>315000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>278100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>419000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>211500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>175800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>193100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>202600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>178900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>248100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>207800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>185400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>244600</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3385,8 +3481,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3424,8 +3520,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3462,15 +3561,15 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>259400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>656300</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3507,53 +3606,56 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1385500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1232300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1412900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1454700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1512900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1143300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1268200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1495500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1449100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1382100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1153700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1449400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1345900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1799100</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3590,71 +3692,74 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9164100</v>
+      </c>
+      <c r="E47" s="3">
         <v>8473000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8608500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8004700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7276400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7172200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6782300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6658700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6266600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6834800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6153300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4806300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5279900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5042200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5329900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>5725800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5515800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6347300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6109000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6915000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3673,52 +3778,55 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>566400</v>
+      </c>
+      <c r="E48" s="3">
         <v>584000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>650900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>566400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>570500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>586200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>298000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
         <v>309300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -3726,18 +3834,18 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3">
         <v>157500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>161900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3756,52 +3864,55 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1085800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1121900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1158000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1194300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>917300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>943200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>969800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1002900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1030500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1058000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1085600</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3809,8 +3920,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,71 +4122,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>896300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1011900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>753200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>946700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>897200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1469200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>837000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1364900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1325000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>664500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>643700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1127400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1144400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1126000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>666800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1016600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1014000</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1013200</v>
       </c>
       <c r="U52" s="3">
         <v>1013200</v>
       </c>
       <c r="V52" s="3">
+        <v>1013200</v>
+      </c>
+      <c r="W52" s="3">
         <v>1298200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,71 +4294,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14027900</v>
+      </c>
+      <c r="E54" s="3">
         <v>13307300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13492900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13019700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11966300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11314000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10535100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10522000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10071300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9939400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9369700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7383000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7770200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7967300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7941700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8596700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8587100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9664300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8962000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10770000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,71 +4446,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>366400</v>
+      </c>
+      <c r="E57" s="3">
         <v>258600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>46900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>443100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>338800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>240000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>45600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>439100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>403700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>277800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>42600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>259900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>186000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>149800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>98200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>225300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>202000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>186800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>134400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>319500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4399,53 +4530,56 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E58" s="3">
         <v>36900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>35500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>316200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>44100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>118200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>78200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>31400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>7600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13500</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4459,19 +4593,19 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>70600</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4482,8 +4616,11 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4505,48 +4642,48 @@
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>230800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>58300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3409800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3547500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3599800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4318800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1004000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1377900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4565,53 +4702,56 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>380200</v>
+      </c>
+      <c r="E60" s="3">
         <v>295400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>266000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>759300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>382900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>358200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>290100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>678900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>424800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>309200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>230100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>267400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>202000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>164600</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4648,71 +4788,74 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3059700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3034400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2379900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2172000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2258200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2058600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1505100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1624900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1433500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1431600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1263900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>569900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>569500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>573400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>444600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>444400</v>
-      </c>
-      <c r="S61" s="3">
-        <v>444000</v>
       </c>
       <c r="T61" s="3">
         <v>444000</v>
       </c>
       <c r="U61" s="3">
+        <v>444000</v>
+      </c>
+      <c r="V61" s="3">
         <v>452900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>256300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4731,53 +4874,56 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6845700</v>
+      </c>
+      <c r="E62" s="3">
         <v>6252800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6710700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6315200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5765700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5398500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5147900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4831100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4906800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4902400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4514500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3506500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3869200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4227800</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,71 +5218,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10285700</v>
+      </c>
+      <c r="E66" s="3">
         <v>9582600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9356600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9246600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8406900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7815300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6943100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7134900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6765000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6643100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6008500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4343800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4640700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4965900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6778400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7445800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7101400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8142900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6355400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5978300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,65 +5680,68 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-406300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-397700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-291600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-294400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-267400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-227100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-187000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-156700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-118500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-59500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-34700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>41300</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5583,8 +5757,8 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA72" s="3">
-        <v>0</v>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB72" s="3">
         <v>0</v>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,71 +6024,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1236000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1133400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1185200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1143500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>991900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>823100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>784100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>723200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>714200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>720400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>579200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>535100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>528200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>509200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1163300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1150900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1485700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1521500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2606600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4791700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>93400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>77100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>67100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>25400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>15500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>26600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>22200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>30000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>41700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>325900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>294800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>890900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>514200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>608200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>323100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>606300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-610000</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,13 +6407,14 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="E83" s="3">
         <v>4800</v>
@@ -6224,53 +6423,53 @@
         <v>4800</v>
       </c>
       <c r="G83" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H83" s="3">
         <v>4600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3">
         <v>16300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6283,8 +6482,8 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,68 +6921,71 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>347700</v>
+      </c>
+      <c r="E89" s="3">
         <v>176500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-43700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>492000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>385900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>198200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-188100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>68900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>214600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>436700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-512000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>692300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>504500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>587300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>84300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>704300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>713600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>417300</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6781,8 +6998,8 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
@@ -6790,8 +7007,11 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,70 +7041,71 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6895,8 +7116,8 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,68 +7297,71 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-516300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-245200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-363000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-57300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7144,8 +7374,8 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,62 +7417,63 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>256600</v>
+      </c>
+      <c r="E96" s="3">
         <v>326900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>251300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>495400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>221500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>260900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>206000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>204800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>210500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>211200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>196700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>95900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>143500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>207100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-183900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-209800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-269200</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,68 +7759,71 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-234300</v>
+      </c>
+      <c r="E100" s="3">
         <v>365100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-201300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-278500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-92800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-177800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-167100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-177300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>14300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>315600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-355600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-538900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-210300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-532300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-209300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-496500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-231100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1170500</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7590,8 +7836,8 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7643,8 +7892,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7682,68 +7931,71 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E102" s="3">
         <v>25400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-254300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-31600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>289900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-356600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>43600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>425700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-559400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>331100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-38500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-175400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>54900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-125200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>205100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>481900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-810500</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7756,13 +8008,16 @@
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>
